--- a/Result/checksun/玻璃陶瓷.xlsx
+++ b/Result/checksun/玻璃陶瓷.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>136.47</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11441,29 +11441,29 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12593,24 +12593,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>10.0</t>
@@ -12623,12 +12623,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -12798,12 +12798,12 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>528</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -14355,12 +14355,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1,861</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">

--- a/Result/checksun/玻璃陶瓷.xlsx
+++ b/Result/checksun/玻璃陶瓷.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/玻璃陶瓷.xlsx
+++ b/Result/checksun/玻璃陶瓷.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,177 +748,177 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12.641</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>29.198</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>39.155</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>39.033</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-700.34</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>40.00000000000057</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>13.33333333333352</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>21.56</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>39.06</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>39.18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>39.027</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-1167.00</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>15.84</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1530819.6</t>
+          <t>1508756.2</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1321494.6</t>
+          <t>1241134.7</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>209325</t>
+          <t>267621</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-71273.59422810333</t>
+          <t>-70646.37074209667</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>177.95</t>
+          <t>-67196.64</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>29.198</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1105,92 +1105,92 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>39.06</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>39.18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>39.027</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-1167.00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>39.16</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>39.2225</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>39.018</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-239.18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>1.960784313725376</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1591029.8</t>
+          <t>1530819.6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1388491.5</t>
+          <t>1321494.6</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>202538</t>
+          <t>209325</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-84264.7843171845</t>
+          <t>-71273.59422810333</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>27380.3</t>
+          <t>177.95</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1352,44 +1352,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>28.29</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>57.446</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1417,14 +1417,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1437,47 +1437,47 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>39.23999999999999</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>39.2725</t>
+          <t>39.2225</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>39.015</t>
+          <t>39.018</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-79.44</t>
+          <t>-239.18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>17.64705882352922</t>
+          <t>1.960784313725376</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1502,27 +1502,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1560482.4</t>
+          <t>1591029.8</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1346314.9</t>
+          <t>1388491.5</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>214167</t>
+          <t>202538</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-104563.8905391784</t>
+          <t>-84264.7843171845</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>69028.89</t>
+          <t>27380.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>57.446</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1739,42 +1739,42 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>39.23999999999999</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>39.2825</t>
+          <t>39.2725</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.005</t>
+          <t>39.015</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-79.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5.882352941176126</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>33.33333333333305</t>
+          <t>17.64705882352922</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1804,32 +1804,32 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1384560.8</t>
+          <t>1560482.4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1217932.7</t>
+          <t>1346314.9</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>166628</t>
+          <t>214167</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-136126.215072793</t>
+          <t>-104563.8905391784</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3487.25</t>
+          <t>69028.89</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1956,177 +1956,177 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>65.26</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>15.282</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>39.31</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>39.2825</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>39.005</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-19.20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>5.882352941176126</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>33.33333333333305</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>13.68</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>39.32</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>39.29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>38.994</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>53.49</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>47.05882352941152</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>43.13725490196049</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-5.40</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>973513.2</t>
+          <t>1384560.8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1029057.8</t>
+          <t>1217932.7</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-55544</t>
+          <t>166628</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-161510.4809844748</t>
+          <t>-136126.215072793</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-124547.4</t>
+          <t>3487.25</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36.302</t>
+          <t>15.282</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2343,42 +2343,42 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>39.29000000000001</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>38.986</t>
+          <t>38.994</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>56.74</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2393,42 +2393,42 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>46.49859943977567</t>
+          <t>43.13725490196049</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1112169.6</t>
+          <t>973513.2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1033896.8</t>
+          <t>1029057.8</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>-55544</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-168231.041181324</t>
+          <t>-161510.4809844748</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-92697.35</t>
+          <t>-124547.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.068</t>
+          <t>36.302</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2645,37 +2645,37 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>39.2925</t>
+          <t>39.29000000000001</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>38.976</t>
+          <t>38.986</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>49.60</t>
+          <t>56.74</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2685,52 +2685,52 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>35.29411764705843</t>
+          <t>47.05882352941152</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>43.31232492997188</t>
+          <t>46.49859943977567</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1185953.2</t>
+          <t>1112169.6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1020673.6</t>
+          <t>1033896.8</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>165279</t>
+          <t>78272</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-181964.4402852067</t>
+          <t>-168231.041181324</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-133363.15</t>
+          <t>-92697.35</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2852,59 +2852,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24.068</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>34.462</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>True</t>
@@ -2947,42 +2947,42 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>39.3175</t>
+          <t>39.2925</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>38.977</t>
+          <t>38.976</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>49.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2992,47 +2992,47 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>57.14285714285705</t>
+          <t>35.29411764705843</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>53.76984126984135</t>
+          <t>43.31232492997188</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1132147.4</t>
+          <t>1185953.2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1116173.9</t>
+          <t>1020673.6</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>165279</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-190801.0385624146</t>
+          <t>-181964.4402852067</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-134308.08</t>
+          <t>-133363.15</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.024</t>
+          <t>34.462</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3199,17 +3199,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -3249,97 +3249,97 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>39.315</t>
+          <t>39.3175</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>38.963</t>
+          <t>38.977</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>40.81</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>37.50000000000015</t>
+          <t>57.14285714285705</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>68.05555555555567</t>
+          <t>53.76984126984135</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1051304.6</t>
+          <t>1132147.4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1177692.4</t>
+          <t>1116173.9</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-126387</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-201072.485901302</t>
+          <t>-190801.0385624146</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-175556.54</t>
+          <t>-134308.08</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3451,12 +3451,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1261.973</t>
+          <t>1149.75</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3501,142 +3501,142 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-3.96</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>20.0325</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20.079</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-55.31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>63.63636363636381</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>50.00000000000023</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-18.44</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-4.75</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>19.22</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>20.1775</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>20.016</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-83.72</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>72.72727272727302</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>28.78787878787895</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-31.60</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>22016484.6</t>
+          <t>23430693.6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>32189347.9</t>
+          <t>28728022.5</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10172863</t>
+          <t>-5297328</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-29679568.80984545</t>
+          <t>-28677194.63399293</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-25388749.02</t>
+          <t>-23164136.67</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1055.488</t>
+          <t>1261.973</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3853,62 +3853,62 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.22</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>20.3175</t>
+          <t>20.1775</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.944</t>
+          <t>20.016</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-137.70</t>
+          <t>-83.72</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13.63636363636381</t>
+          <t>72.72727272727302</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>20.41847041847048</t>
+          <t>28.78787878787895</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-33.05</t>
+          <t>-31.60</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -3918,27 +3918,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>22775545.8</t>
+          <t>22016484.6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>34017187.4</t>
+          <t>32189347.9</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11241641</t>
+          <t>-10172863</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-30459717.86300306</t>
+          <t>-29679568.80984545</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>-27883914.87</t>
+          <t>-25388749.02</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1323.246</t>
+          <t>1055.488</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4155,62 +4155,62 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>20.5225</t>
+          <t>20.3175</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19.872</t>
+          <t>19.944</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-244.06</t>
+          <t>-137.70</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.63636363636381</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>20.47071702244115</t>
+          <t>20.41847041847048</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-33.05</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -4220,27 +4220,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>27831995.4</t>
+          <t>22775545.8</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>37628858.3</t>
+          <t>34017187.4</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-9796862</t>
+          <t>-11241641</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-30928045.67901073</t>
+          <t>-30459717.86300306</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>-30003964.5</t>
+          <t>-27883914.87</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1297.066</t>
+          <t>1323.246</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4387,17 +4387,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4457,52 +4457,52 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>20.785</t>
+          <t>20.5225</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19.802</t>
+          <t>19.872</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-673.20</t>
+          <t>-244.06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>47.61904761904759</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -4522,27 +4522,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>29565808.0</t>
+          <t>27831995.4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>38718702.7</t>
+          <t>37628858.3</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-9152894</t>
+          <t>-9796862</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-31096060.43932933</t>
+          <t>-30928045.67901073</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>-32517759.4</t>
+          <t>-30003964.5</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>791.74</t>
+          <t>1297.066</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4689,17 +4689,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4734,17 +4734,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4759,62 +4759,62 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.785</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19.709</t>
+          <t>19.802</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1205.82</t>
+          <t>-673.20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>13.79310344827582</t>
+          <t>47.61904761904759</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>8.89877641824247</t>
+          <t>20.47071702244115</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>-14.68</t>
+          <t>-23.64</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -4824,27 +4824,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>34025351.4</t>
+          <t>29565808.0</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>39878605.1</t>
+          <t>38718702.7</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5853253</t>
+          <t>-9152894</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-30837569.71844194</t>
+          <t>-31096060.43932933</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>-34934368.19</t>
+          <t>-32517759.4</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1476.285</t>
+          <t>791.74</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -5061,62 +5061,62 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>21.075</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19.629</t>
+          <t>19.709</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-336.66</t>
+          <t>-1205.82</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79310344827582</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4.301075268817196</t>
+          <t>8.89877641824247</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-14.68</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -5126,27 +5126,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>42362211.2</t>
+          <t>34025351.4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>43752241.2</t>
+          <t>39878605.1</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1390030</t>
+          <t>-5853253</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-30092697.26990067</t>
+          <t>-30837569.71844194</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>-36062583.65</t>
+          <t>-34934368.19</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2318.423</t>
+          <t>1476.285</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5293,162 +5293,162 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>-2.06</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>-7.95</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>7.37</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>19.4</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>21.075</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19.629</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-336.66</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>4.301075268817196</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>-3.18</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>-0.92</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>-7.74</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>8.56</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>21.2225</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>19.549</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>-190.17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>12.90322580645156</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>4.301075268817196</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>-4.61</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>45258829.0</t>
+          <t>42362211.2</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>47443725.3</t>
+          <t>43752241.2</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2184896</t>
+          <t>-1390030</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-29007263.38225489</t>
+          <t>-30092697.26990067</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>-37774511.76</t>
+          <t>-36062583.65</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1767.687</t>
+          <t>2318.423</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5665,62 +5665,62 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>21.3725</t>
+          <t>21.2225</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19.461</t>
+          <t>19.549</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-140.04</t>
+          <t>-190.17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.90322580645156</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1.923076923076959</t>
+          <t>4.301075268817196</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -5730,27 +5730,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>47425721.2</t>
+          <t>45258829.0</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>57809124.0</t>
+          <t>47443725.3</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-10383402</t>
+          <t>-2184896</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-27413218.22276839</t>
+          <t>-29007263.38225489</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>-40724587.06</t>
+          <t>-37774511.76</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2433.338</t>
+          <t>1767.687</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5917,142 +5917,142 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>-7.87</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>9.82</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>21.3725</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19.461</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-140.04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>1.923076923076959</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>-17.96</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>-2.96</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>-7.23</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>21.495</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>19.373</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>-104.50</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>1.923076923076959</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>-29.17</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>47871597.4</t>
+          <t>47425721.2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>67585345.0</t>
+          <t>57809124.0</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-19713747</t>
+          <t>-10383402</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-24992969.34246812</t>
+          <t>-27413218.22276839</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>-42261269.46</t>
+          <t>-40724587.06</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2424.223</t>
+          <t>1320.274</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -6239,22 +6239,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6269,37 +6269,37 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>19.435</t>
+          <t>19.4475</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.949</t>
+          <t>19.006</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-54.65</t>
+          <t>-39.98</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.69230769230766</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>33.33333333333332</t>
+          <t>52.56410256410254</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -6334,27 +6334,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>21408682.6</t>
+          <t>24029811.0</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26179392.5</t>
+          <t>27146722.3</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4770709</t>
+          <t>-3116911</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4195659.689302529</t>
+          <t>-3904385.068910175</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>-2454084.87</t>
+          <t>-2302374.66</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>514.929</t>
+          <t>2424.223</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6541,22 +6541,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6571,62 +6571,62 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>19.4025</t>
+          <t>19.435</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.874</t>
+          <t>18.949</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-120.66</t>
+          <t>-54.65</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>14.28571428571425</t>
+          <t>33.33333333333332</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>-20.57</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -6636,27 +6636,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>19117578.4</t>
+          <t>21408682.6</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>24069293.4</t>
+          <t>26179392.5</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4951715</t>
+          <t>-4770709</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4512309.657009557</t>
+          <t>-4195659.689302529</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>-4908198.81</t>
+          <t>-2454084.87</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>792.093</t>
+          <t>514.929</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6803,17 +6803,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6843,92 +6843,92 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-1.83</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>19.4025</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18.874</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-120.66</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>-2.18</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>19.4475</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>-84.91</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>38.09523809523796</t>
+          <t>14.28571428571425</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>-20.57</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -6938,27 +6938,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>30604071.4</t>
+          <t>19117578.4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>27898340.9</t>
+          <t>24069293.4</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2705730</t>
+          <t>-4951715</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4440329.810146745</t>
+          <t>-4512309.657009557</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>-4199490.39</t>
+          <t>-4908198.81</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1151.215</t>
+          <t>792.093</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7105,17 +7105,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -7150,17 +7150,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>-14.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7175,62 +7175,62 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>19.5075</t>
+          <t>19.4475</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.769</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-60.86</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>42.85714285714278</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>57.14285714285703</t>
+          <t>38.09523809523796</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -7240,27 +7240,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>31264692.0</t>
+          <t>30604071.4</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>30663460.0</t>
+          <t>27898340.9</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>601232</t>
+          <t>2705730</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-4484118.795679716</t>
+          <t>-4440329.810146745</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>-3615154.27</t>
+          <t>-4199490.39</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>646.892</t>
+          <t>1151.215</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7407,17 +7407,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -7447,22 +7447,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-14.0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7477,62 +7477,62 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>19.5175</t>
+          <t>19.5075</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18.682</t>
+          <t>18.769</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-54.31</t>
+          <t>-60.86</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>71.42857142857115</t>
+          <t>42.85714285714278</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>68.78306878306874</t>
+          <t>57.14285714285703</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -7542,27 +7542,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>30263633.6</t>
+          <t>31264692.0</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>31041945.0</t>
+          <t>30663460.0</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-778311</t>
+          <t>601232</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-4642112.346058293</t>
+          <t>-4484118.795679716</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>-3423391.09</t>
+          <t>-3615154.27</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1826.39</t>
+          <t>646.892</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7709,17 +7709,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7779,62 +7779,62 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>19.5425</t>
+          <t>19.5175</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18.598</t>
+          <t>18.682</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-55.94</t>
+          <t>-54.31</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>57.14285714285722</t>
+          <t>71.42857142857115</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>44.97354497354502</t>
+          <t>68.78306878306874</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>30950102.4</t>
+          <t>30263633.6</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>32159506.2</t>
+          <t>31041945.0</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-1209403</t>
+          <t>-778311</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-4863698.029709027</t>
+          <t>-4642112.346058293</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>-1987063.86</t>
+          <t>-3423391.09</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3381.704</t>
+          <t>1826.39</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -8051,22 +8051,22 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -8101,42 +8101,42 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.5425</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18.518</t>
+          <t>18.598</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-53.78</t>
+          <t>-55.94</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>77.77777777777791</t>
+          <t>57.14285714285722</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>25.92592592592596</t>
+          <t>44.97354497354502</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -8146,27 +8146,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>29021008.4</t>
+          <t>30950102.4</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>30867417.9</t>
+          <t>32159506.2</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-1846409</t>
+          <t>-1209403</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-5386722.424612561</t>
+          <t>-4863698.029709027</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>-2366030.89</t>
+          <t>-1987063.86</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>973.662</t>
+          <t>3381.704</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8383,17 +8383,17 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>19.6275</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18.446</t>
+          <t>18.518</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-61.47</t>
+          <t>-53.78</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.77777777777791</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>5.555555555555498</t>
+          <t>25.92592592592596</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>-13.14</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -8448,27 +8448,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>25192610.4</t>
+          <t>29021008.4</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>29004005.7</t>
+          <t>30867417.9</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-3811395</t>
+          <t>-1846409</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-5935939.066559116</t>
+          <t>-5386722.424612561</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>-6164474.24</t>
+          <t>-2366030.89</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>902.143</t>
+          <t>973.662</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8615,17 +8615,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8685,47 +8685,47 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>19.6975</t>
+          <t>19.6275</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.446</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-49.04</t>
+          <t>-61.47</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-13.14</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -8750,27 +8750,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>30062228.0</t>
+          <t>25192610.4</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>31358981.5</t>
+          <t>29004005.7</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-1296753</t>
+          <t>-3811395</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-5894387.217737705</t>
+          <t>-5935939.066559116</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>-6149173.86</t>
+          <t>-6164474.24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>289.178</t>
+          <t>355.789</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8917,17 +8917,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8937,142 +8937,142 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-4.53</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>9.346</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>9.433499999999999</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>9.8808</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>8.70</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>18.74999999999958</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>10.41666666666644</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>-11.05</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-4.41</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>9.366</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>9.4585</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>9.895199999999999</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>12.49999999999972</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>4.166666666666575</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>-13.47</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>2791958.8</t>
+          <t>3017968.2</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>3226550.7</t>
+          <t>3392903.2</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-434591</t>
+          <t>-374935</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-657491.4373518439</t>
+          <t>-628957.7762699241</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>-544208.46</t>
+          <t>-472022.64</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>315.481</t>
+          <t>289.178</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9219,17 +9219,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -9289,37 +9289,37 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>9.382</t>
+          <t>9.366</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>9.4875</t>
+          <t>9.4585</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9.9084</t>
+          <t>9.895199999999999</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -9329,22 +9329,22 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.49999999999972</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>11.11111111111095</t>
+          <t>4.166666666666575</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-13.47</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -9354,27 +9354,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>2852067.4</t>
+          <t>2791958.8</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>3292155.1</t>
+          <t>3226550.7</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-440087</t>
+          <t>-434591</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-678088.3414592099</t>
+          <t>-657491.4373518439</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>-560684.66</t>
+          <t>-544208.46</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>373.947</t>
+          <t>315.481</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9521,17 +9521,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -9571,82 +9571,82 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>9.382</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>9.4875</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>9.9084</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>9.414</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>9.5225</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>9.924399999999999</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>9.71</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>24.99999999999963</t>
+          <t>11.11111111111095</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -9656,27 +9656,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>3429904.8</t>
+          <t>2852067.4</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>3598533.7</t>
+          <t>3292155.1</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-168628</t>
+          <t>-440087</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-699434.4650606599</t>
+          <t>-678088.3414592099</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>-589899.71</t>
+          <t>-560684.66</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>275.545</t>
+          <t>373.947</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9823,17 +9823,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9893,42 +9893,42 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>9.432</t>
+          <t>9.414</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>9.544</t>
+          <t>9.5225</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9.934800000000001</t>
+          <t>9.924399999999999</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>33.33333333333284</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>30.55555555555511</t>
+          <t>24.99999999999963</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -9958,27 +9958,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>3493375.8</t>
+          <t>3429904.8</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>3471824.0</t>
+          <t>3598533.7</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>-168628</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-719349.8759796142</t>
+          <t>-699434.4650606599</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>-671517.99</t>
+          <t>-589899.71</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>233.269</t>
+          <t>275.545</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -10195,37 +10195,37 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>9.424</t>
+          <t>9.432</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>9.560500000000001</t>
+          <t>9.544</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>9.939</t>
+          <t>9.934800000000001</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -10235,22 +10235,22 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>41.66666666666605</t>
+          <t>33.33333333333284</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>41.66666666666655</t>
+          <t>30.55555555555511</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -10260,27 +10260,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>3767838.2</t>
+          <t>3493375.8</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>3598819.2</t>
+          <t>3471824.0</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>169019</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-728046.5822007121</t>
+          <t>-719349.8759796142</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>-667251.62</t>
+          <t>-671517.99</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>319.08</t>
+          <t>233.269</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10472,24 +10472,24 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
           <t>289</t>
@@ -10497,42 +10497,42 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>9.426</t>
+          <t>9.424</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>9.575</t>
+          <t>9.560500000000001</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>9.948</t>
+          <t>9.939</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -10542,17 +10542,17 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>16.66666666666642</t>
+          <t>41.66666666666605</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>47.22222222222202</t>
+          <t>41.66666666666655</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -10562,27 +10562,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>3661142.6</t>
+          <t>3767838.2</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>3719427.9</t>
+          <t>3598819.2</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-58285</t>
+          <t>169019</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-739100.212419652</t>
+          <t>-728046.5822007121</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>-593689.02</t>
+          <t>-667251.62</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>612.477</t>
+          <t>319.08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10729,17 +10729,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -10799,62 +10799,62 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>9.436</t>
+          <t>9.426</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.575</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9.957</t>
+          <t>9.948</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
           <t>-0.19</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>66.66666666666717</t>
+          <t>16.66666666666642</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>41.66666666666654</t>
+          <t>47.22222222222202</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -10864,27 +10864,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>3732242.8</t>
+          <t>3661142.6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>3822224.8</t>
+          <t>3719427.9</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>-89982</t>
+          <t>-58285</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>-765538.6107737104</t>
+          <t>-739100.212419652</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>-553463.53</t>
+          <t>-593689.02</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>405.461</t>
+          <t>612.477</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11031,17 +11031,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -11101,62 +11101,62 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>9.443999999999999</t>
+          <t>9.436</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>9.629499999999998</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9.9668</t>
+          <t>9.957</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
           <t>-0.20</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>58.33333333333247</t>
+          <t>66.66666666666717</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>27.02020202020161</t>
+          <t>41.66666666666654</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>-18.65</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -11166,27 +11166,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>3767162.6</t>
+          <t>3732242.8</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>4630889.2</t>
+          <t>3822224.8</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>-863726</t>
+          <t>-89982</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>-804097.7166365638</t>
+          <t>-765538.6107737104</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>-779288.77</t>
+          <t>-553463.53</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -11303,12 +11303,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>423.439</t>
+          <t>405.461</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -11403,37 +11403,37 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>9.447999999999999</t>
+          <t>9.443999999999999</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>9.662</t>
+          <t>9.629499999999998</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9.9758</t>
+          <t>9.9668</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -11448,17 +11448,17 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.33333333333247</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>14.02737047898315</t>
+          <t>27.02020202020161</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>-28.63</t>
+          <t>-18.65</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -11468,27 +11468,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>3450272.2</t>
+          <t>3767162.6</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>4834040.5</t>
+          <t>4630889.2</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>-1383768</t>
+          <t>-863726</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>-808608.4342556538</t>
+          <t>-804097.7166365638</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>-859461.44</t>
+          <t>-779288.77</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>142240.677</t>
+          <t>256083.226</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11635,17 +11635,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>31.24</t>
+          <t>56.24</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -11675,22 +11675,22 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11705,47 +11705,47 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>27.135</t>
+          <t>27.3525</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>28.168</t>
+          <t>28.354</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>135.91</t>
+          <t>515.68</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>69.69696969696972</t>
+          <t>89.09090909090908</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
@@ -11770,32 +11770,32 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>2605268838.4</t>
+          <t>3896887336.0</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>2538920477.7</t>
+          <t>3241746609.8</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>66348360</t>
+          <t>655140726</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>-15231133.21837565</t>
+          <t>66875317.8269087</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>138047657.87</t>
+          <t>518460798.58</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -11815,12 +11815,12 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11922,12 +11922,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>47148.923</t>
+          <t>142240.677</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11937,17 +11937,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>31.24</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -11977,22 +11977,22 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -12007,62 +12007,62 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>26.99</t>
+          <t>27.135</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>27.972</t>
+          <t>28.168</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>135.91</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>67.27272727272732</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>60.92503987240831</t>
+          <t>69.69696969696972</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -12072,32 +12072,32 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>2504452842.0</t>
+          <t>2605268838.4</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>2384349720.1</t>
+          <t>2538920477.7</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>120103121</t>
+          <t>66348360</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>-43100004.32595558</t>
+          <t>-15231133.21837565</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>-8637720.8</t>
+          <t>138047657.87</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12224,12 +12224,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>79981.971</t>
+          <t>47148.923</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12239,17 +12239,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -12279,22 +12279,22 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -12309,62 +12309,62 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>26.9825</t>
+          <t>26.99</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>27.821</t>
+          <t>27.972</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>41.81818181818189</t>
+          <t>67.27272727272732</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>56.62945241892609</t>
+          <t>60.92503987240831</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>3326728521.0</t>
+          <t>2504452842.0</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>2334310904.8</t>
+          <t>2384349720.1</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>992417616</t>
+          <t>120103121</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>-49365874.05712376</t>
+          <t>-43100004.32595558</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>97944695.22</t>
+          <t>-8637720.8</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -12419,12 +12419,12 @@
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -12516,59 +12516,59 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>79981.971</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>17.57</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-5.34</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>11.29</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>132446.347</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>29.09</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>27.95</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>8.51</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>False</t>
@@ -12581,22 +12581,22 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12611,42 +12611,42 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>27.0775</t>
+          <t>26.9825</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>27.648</t>
+          <t>27.821</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -12656,17 +12656,17 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>73.68421052631578</t>
+          <t>41.81818181818189</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>48.15453935384906</t>
+          <t>56.62945241892609</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>42.51</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
@@ -12676,32 +12676,32 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>3083990078.4</t>
+          <t>3326728521.0</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>2173799273.1</t>
+          <t>2334310904.8</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>910190805</t>
+          <t>992417616</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>-76149613.925717</t>
+          <t>-49365874.05712376</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>147920866.0</t>
+          <t>97944695.22</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -12813,12 +12813,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>56170.472</t>
+          <t>132446.347</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12843,17 +12843,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -12883,22 +12883,22 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>71</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-13.0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12913,62 +12913,62 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>27.1175</t>
+          <t>27.0775</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>27.425</t>
+          <t>27.648</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>54.38596491228063</t>
+          <t>73.68421052631578</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>56.92646917841046</t>
+          <t>48.15453935384906</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>2586605883.6</t>
+          <t>3083990078.4</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>1879696126.7</t>
+          <t>2173799273.1</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>706909756</t>
+          <t>910190805</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>-116889701.1844873</t>
+          <t>-76149613.925717</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>49010996.75</t>
+          <t>147920866.0</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -13115,12 +13115,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>138317.415</t>
+          <t>56170.472</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -13145,17 +13145,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -13185,22 +13185,22 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -13215,62 +13215,62 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>27.34249999999999</t>
+          <t>27.1175</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>27.214</t>
+          <t>27.425</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>-50.88</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>16.39344262295081</t>
+          <t>54.38596491228063</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>65.18670309653915</t>
+          <t>56.92646917841046</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
@@ -13280,27 +13280,27 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>2472572117.0</t>
+          <t>2586605883.6</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>1836443532.6</t>
+          <t>1879696126.7</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>636128584</t>
+          <t>706909756</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>-147053464.4454866</t>
+          <t>-116889701.1844873</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>144190475.59</t>
+          <t>49010996.75</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -13325,12 +13325,12 @@
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>189245.112</t>
+          <t>138317.415</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -13447,17 +13447,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -13487,22 +13487,22 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13517,62 +13517,62 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.34249999999999</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>27.214</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>-52.35</t>
+          <t>-50.88</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>16.39344262295081</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>68.05555555555556</t>
+          <t>65.18670309653915</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
@@ -13582,27 +13582,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>2264246598.2</t>
+          <t>2472572117.0</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>1609754402.1</t>
+          <t>1836443532.6</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>654492196</t>
+          <t>636128584</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>-200006908.0876323</t>
+          <t>-147053464.4454866</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>38773827.12</t>
+          <t>144190475.59</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38047.337</t>
+          <t>189245.112</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -13749,17 +13749,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -13819,62 +13819,62 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>28.0925</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>26.799</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>-159.20</t>
+          <t>-52.35</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>79.16666666666671</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>51.74349881796693</t>
+          <t>68.05555555555556</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
@@ -13884,27 +13884,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>1341893288.6</t>
+          <t>2264246598.2</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>1352492197.4</t>
+          <t>1609754402.1</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>-10598908</t>
+          <t>654492196</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>-243421587.2155312</t>
+          <t>-200006908.0876323</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>-291895095.1</t>
+          <t>38773827.12</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14036,12 +14036,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>47917.497</t>
+          <t>38047.337</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -14051,17 +14051,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -14121,62 +14121,62 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>28.4775</t>
+          <t>28.0925</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>26.614</t>
+          <t>26.799</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>-342.71</t>
+          <t>-159.20</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>79.16666666666671</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>32.41343345848981</t>
+          <t>51.74349881796693</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>-26.26</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
@@ -14186,27 +14186,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>1263608467.8</t>
+          <t>1341893288.6</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>1713713937.6</t>
+          <t>1352492197.4</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>-450105469</t>
+          <t>-10598908</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>-234608222.1463212</t>
+          <t>-243421587.2155312</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>-282097564.15</t>
+          <t>-291895095.1</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">

--- a/Result/checksun/玻璃陶瓷.xlsx
+++ b/Result/checksun/玻璃陶瓷.xlsx
@@ -11838,7 +11838,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -11918,109 +11918,109 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>2025-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>-3.73</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>9.169999999999998</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>9.239</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>9.5966</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>10.74</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>2025-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>10.45</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>-3.73</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>9.169999999999998</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>9.239</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>9.5966</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR32" t="inlineStr">
         <is>
           <t>36.84210526315783</t>
@@ -12093,62 +12093,62 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -12330,12 +12330,12 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -12460,62 +12460,62 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -12827,62 +12827,62 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -12897,12 +12897,12 @@
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -13194,62 +13194,62 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="BT35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -13431,12 +13431,12 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -13561,62 +13561,62 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
@@ -13631,12 +13631,12 @@
       </c>
       <c r="BT36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -13753,109 +13753,109 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>2025-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2025-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>11.45</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>10.45</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>-4.23</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>9.134</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>9.3055</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>9.7166</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-05-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2025-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2025-07-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>11.45</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>10.45</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>9.134</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>9.3055</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>9.7166</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR37" t="inlineStr">
         <is>
           <t>4.761904761904923</t>
@@ -13928,62 +13928,62 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="BT37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -14165,12 +14165,12 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -14295,62 +14295,62 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
@@ -14365,12 +14365,12 @@
       </c>
       <c r="BT38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -14407,7 +14407,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -14657,67 +14657,67 @@
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="BT39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -14899,12 +14899,12 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -15029,62 +15029,62 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
@@ -15099,12 +15099,12 @@
       </c>
       <c r="BT40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -15396,62 +15396,62 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.01639344262295</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23.39391825395837</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0118110013157716</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BL41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="BM41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.94%</t>
         </is>
       </c>
       <c r="BN41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="BO41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>瓷磚94.53%、營建5.27%、木地板0.21% (2024年)</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="BT41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="BU41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 建材營造 - 建材原料</t>
         </is>
       </c>
     </row>

--- a/Result/checksun/玻璃陶瓷.xlsx
+++ b/Result/checksun/玻璃陶瓷.xlsx
@@ -1011,15 +1011,11 @@
           <t>38.6225</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>39.006</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>38.9175</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>39.006</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>38.9175</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>38.685</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>39.022</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>38.933125</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>39.022</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>38.933125</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>38.7475</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>39.038</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>38.955</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>39.038</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>38.955</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>38.8</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>39.056</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>38.980625</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>39.056</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>38.980625</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>38.8525</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>39.07</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>39.00375</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>39.00375</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>38.8875</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>39.053</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>39.02625</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>39.053</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>39.02625</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>38.9325</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>39.036</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>39.044375</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>39.036</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>39.044375</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>38.9975</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>39.03299999999999</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>39.09625</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>39.03299999999999</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>39.09625</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>39.033</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>39.138125</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>39.033</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>39.138125</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>39.045</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>39.036</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>39.17999999999999</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>39.036</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>39.17999999999999</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>18.9225</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>20.143</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>18.888125</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>20.143</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>18.888125</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>18.9875</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>20.218</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>18.84625</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>20.218</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>18.84625</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>19.035</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>20.271</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>18.8025</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>20.271</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>18.8025</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>19.1</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>20.317</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>18.7625</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>20.317</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>18.7625</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>19.145</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>18.71875</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>18.71875</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>19.1875</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>18.674375</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>18.674375</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>19.2525</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>20.399</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>18.628125</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>20.399</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>18.628125</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>19.3</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>20.386</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>18.583125</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>20.386</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>18.583125</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>19.3575</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>20.376</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>18.54</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>20.376</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>18.54</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>19.44</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>20.366</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>18.496875</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>20.366</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>18.496875</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>19.1525</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>19.468</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>19.468</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>18.39</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>19.205</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>19.54</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>18.351875</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>18.351875</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>19.2525</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>19.596</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>18.3175</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>19.596</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>18.3175</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>19.2925</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>19.626</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>18.283125</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>19.626</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>18.283125</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>19.2875</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>19.633</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>18.2425</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>19.633</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>18.2425</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>19.2825</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>19.601</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>18.198125</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>19.601</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>18.198125</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>19.295</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>19.547</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>18.153125</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>19.547</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>18.153125</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>19.29</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>19.482</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>18.11</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>19.482</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>18.11</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>19.32</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>19.425</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>18.070625</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>19.425</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>18.070625</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>19.355</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>19.378</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>18.030625</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>19.378</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>18.030625</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>9.2035</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>9.537</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>9.754499999999998</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>9.537000000000001</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>9.754499999999998</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>9.221</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>9.5674</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>9.766625000000001</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>9.567399999999999</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>9.766624999999999</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>9.239</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>9.5966</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>9.78425</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>9.5966</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>9.78425</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>9.258000000000001</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>9.623000000000001</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>9.80825</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>9.622999999999999</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>9.808249999999999</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>9.275</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>9.6518</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>9.843125</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>9.6518</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>9.843125000000001</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>9.28</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>9.6712</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>9.872125</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>9.671200000000001</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>9.872125</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>9.294</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>9.692</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>9.905125000000002</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>9.692</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>9.905125000000002</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>9.3055</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>9.7166</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>9.938625</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>9.7166</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>9.938625</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>9.326</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>9.7438</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>9.973125</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>9.7438</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>9.973125</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>9.3445</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>9.7708</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>10.0025</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>9.770799999999999</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>10.0025</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>28.7575</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>29.069</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>26.42312500000001</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>29.069</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>26.42312500000001</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>28.7275</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>29.257</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>26.273125</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>29.257</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>26.273125</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>28.635</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>29.377</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>26.126875</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>29.377</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>26.126875</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>28.6625</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>29.433</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>25.98125</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>29.433</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>25.98125</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>28.545</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>29.451</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>29.451</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>25.82</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>28.4275</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>29.428</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>25.664375</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>29.428</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>25.664375</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>28.38750000000001</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>29.369</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>25.51875</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>29.369</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>25.51875</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>28.325</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>29.292</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>25.37125</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>29.292</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>25.37125</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>28.2125</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>29.196</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>25.2225</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>29.196</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>25.2225</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>28.11</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>29.103</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>25.07375</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>29.103</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>25.07375</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>

--- a/Result/checksun/玻璃陶瓷.xlsx
+++ b/Result/checksun/玻璃陶瓷.xlsx
@@ -5568,7 +5568,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>1810</t>
@@ -5992,7 +5996,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6418,7 +6422,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6844,7 +6848,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7270,7 +7274,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7696,7 +7700,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8120,7 +8124,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>1810</t>
@@ -8542,7 +8550,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>1810</t>
@@ -8964,7 +8976,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>1810</t>
@@ -10238,7 +10254,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>1809</t>
@@ -10662,7 +10682,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>1809</t>
@@ -11086,7 +11110,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>1809</t>
@@ -11510,7 +11538,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>1809</t>
@@ -11934,7 +11966,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>1809</t>
@@ -12358,7 +12394,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>1809</t>
@@ -14924,7 +14964,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15350,7 +15390,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15776,7 +15816,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16202,7 +16242,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16628,7 +16668,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17054,7 +17094,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17478,7 +17518,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>1806</t>
@@ -17900,7 +17944,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>1806</t>
@@ -18322,7 +18370,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>1806</t>
